--- a/pacjenci/KATARZYNA BARCZYK.xlsx
+++ b/pacjenci/KATARZYNA BARCZYK.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -529,7 +529,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,12 +573,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,11 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -655,7 +659,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -695,7 +703,11 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -735,7 +747,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/KATARZYNA BARCZYK.xlsx
+++ b/pacjenci/KATARZYNA BARCZYK.xlsx
@@ -413,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -452,328 +452,236 @@
           <t>SUVmax</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>20.09.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>HL. Ocena przed leczeniem.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 95 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywna metabolicznie masa miękkotkankowa w śródpiersiu pośrodkowo i po stronie lewej o największych wymiarach 65 mm [Im fuz.99]x78 [Im fuz. 108]x112 mm SUV max do 15,2.  Aktywne metabolicznie węzły chłonne: - śródpiersiowe najwyższe wielkości do 17 mm SUV max do 12,0 - zamostkowy wielkości 15x11 mm SUV max 7,2 - wnęki płuca lewego wielkości 17x11 mm SUV max 10,3 - śródpiersiowy lewy średnicy 10 mm SUV max 7,2 - przyosierdziowy prawy wielkości 5x12 mm SUV max 4,9 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwłóknienia w nadprzeponowych partiach płuc.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 6,9- odczynowo? Pobudzenie metaboliczne w macicy SUV max do 4,3- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Sklerotyczny obszar wielkości mm  w trzonie Th 5 pośrodkowo - zawał kostny ? Dyskopatia C5/6.  Wartości referencyjne: MBPS SUVmax 2,1 Prawy płat wątroby SUVmax do 4,6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem węzłów chłonnych śródpiersia i klatki piersiowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>15.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>15.11.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>HL w trakcie chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu pośrodkowo i po stronie lewej, o wymiarach 52x23mm, SUV max 3,9, z podejrzeniem obecności płynu w worku osierdziowym, w części górno-lewobocznej, o szerokości płaszcza do 13mm lub z jego naciekiem przez chorobę zasadniczą - dokładna ocena w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku - odczynowo? Pobudzenie metaboliczne w macicy - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym, wielkości 10x8mm.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem-związane ze stosowanym leczeniem?. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny ? . Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm, SUV max do 2,3-do ew. kontroli.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 4,5.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź procesu chłoniakowego na stosowane leczenie.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.5</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>15.03.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>HL. Ocena po leczeniu 2xBEACOPP esc. + 2xABVD. Stan po radioterapii śródpiersia.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 103mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Symetryczna aktywność metaboliczna w topografii migdałków podniebiennych, SUV max do 6,9. Drobny aktywny metabolicznie węzeł chłonny grupy 2A po stronie lewej średnicy wg PET 10mm, SUV max 3,8 - odczynowy? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie lewej, o wymiarach 48x15mm (SUV max 2,8). Drobne zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku, SUV max 7,9 - odczynowo? Aktywny metabolicznie obszary w poprzecznicy średnicy wg PET 15mm i 15mm, SUV max 7,7 - do rozważenia ocena endoskopowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym, wielkości 10x8mm.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?   Wartości referencyjne: MBPS SUVmax do 2,8; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnego metabolicznie procesu chłoniakowego. Masy resztkowe do kontroli.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>7.9</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>21.06.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>HSCHL. Ocena kontrolna 11 m-cy o zakończeniu terapii - planowana operacja bariatryczna.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 92 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Symetrycznie wzmożona aktywność metaboliczna w topografii migdałków gardłowych, SUV max do 4,9. Aktywny metabolicznie węzeł chłonny szyjny grupy 2A po stronie lewej, średnicy 8 mm SUV max 4,3 - odczynowy? inny? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie lewej, z tendencją do defragmentacji, wielkości do 19x12mm (SUV max 2,1). Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne- do kontroli. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max 5,2- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x8mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?   Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 4,1.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnego metabolicznie węzła chłonnego szyjnego grupy 2A  - odczynowy? inny? - niejednorodnego metabolizmu FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne - do kontroli. Masy resztkowe w śródpiersiu - do kontroli.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.2</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>08.05.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>HSCHL. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Symetrycznie wzmożona aktywność metaboliczna w topografii migdałków gardłowych, SUV max do 4,9. Aktywne metabolicznie węzły chłonne szyjne grupy 2A: po stronie lewej, średnicy 12mm SUV max 5,3, po stronie prawej średnicy 10mm, SUV max 4,4 - odczynowe? inne? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy średnicy wg PET 18mm, SUV max 9,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pobudzone metabolicznie węzeł chłonny położone przy łuku aorty średnicy wg PET do 7mm, SUV max do 2,9 [lm fuz 93] - poniżej wartości referencyjnych W śródpiersiu po stronie lewej drobne węzły chłonne wielkości do 7mm, resztkowa grasica o grubości do 8mm. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne- do kontroli. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max do 8,0 - odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x8mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?   Wartości referencyjne: MBPS SUVmax do 3,1; Prawy płat wątroby SUVmax do 4,3.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywne metabolicznie węzły chłonne szyjne grup 2A  - odczynowe?  - pobudzone metabolicznie węzły chłonne położone przy łuku aorty oraz pojedynczy aktywny metabolicznie węzeł chłonny podostrogowy - do  weryfikacji/kontroli. Masy resztkowe w śródpiersiu - do kontroli.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>9.9</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>02.11.2023</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>HSCHL. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 97 mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Wzmożona aktywność metaboliczna w topografii migdałka gardłowego, SUV max do 5,9. Miernie pobudzone metabolicznie węzły chłonne szyjne grupy 2A obustronnie średnicy do 9mm, SUV max 3,3 - odczynowe? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy wielkości 22x16mm, SUV max 10,2. Nadal widoczne niejednorodny metabolizm FDG w sercu jak w badaniu przednim  - do kontroli w echokardiografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu po stronie lewej drobne węzły chłonne wielkości do 7mm, resztkowa grasica o grubości do 8mm - jak poprzednio. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x7mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 2,8; Prawy płat wątroby SUVmax do 3,9.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzone metabolicznie węzły chłonne szyjne grup 2A  - odczynowe?  - aktywny metabolicznie węzeł chłonny podostrogowy - do  weryfikacji/kontroli. Masy resztkowe w śródpiersiu - jak w poprzednim badaniu PET/CT z dnia 8.05.2023r</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>10.2</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>09.05.2024</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>HSCHL. Utrzymująca się aktywność w węźle podostrogowym- EBUS ujemny. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 101mg%.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Zwiększona aktywność metaboliczna na tylnej ścianie nosogardła, SUV max 8,5- do kontroli larynoglogicznej. Miernie pobudzone metabolicznie węzły chłonne szyjne grupy 2A obustronnie, średnicy do 9mm, SUV max 3,8 - odczynowe? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy wielkości 15x12mm, SUV max 7,9- niewielka regresja metaboliczna. Pobudzony metabolicznie węzeł chłonny w śródpiersiu po stronie lewej, wielkości 15x10mm, SUV max 3,6 (poprzednio z miernym pobudzeniem metabolicznym, SUV max 2,1). Pobudzony metabolicznie obszar miąższowo-włóknisto-guzkowy w segmencie 4 płuca lewego, wielkości ok. 13x10mm wg PET, SUV max 5,1 - do weryfikacji.  Nadal widoczny jest niejednorodny metabolizm FDG w sercu jak w badaniu przednim  - do kontroli w Echokardiografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poza powyższym w śródpiersiu przednim drobne węzły chłonne wielkości do 9mm. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby. Rozlanie wzmożony metabolizm FDG w żołądku - odczynowo? Odcinkowo zwiększona aktywnośc metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x7mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 2,7; Prawy płat wątroby SUVmax do 4,5.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzonych metabolicznie węzłów chłonnych szyjnych grup 2A  - odczynowe?  - aktywnego metabolicznie węzła chłonnego podostrogowo - niewielka regresja metaboliczna w stosunku do badania z 9.05.2024 - pobudzonego metabolicznie węzła chłonnego w śródpiersiu po stronie lewej. Pobudzony metabolicznie obszar miąższowo-włóknisto-guzkowy w segmencie 4 płuca lewego - do weryfikacji.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>8.5</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/KATARZYNA BARCZYK.xlsx
+++ b/pacjenci/KATARZYNA BARCZYK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 95 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywna metabolicznie masa miękkotkankowa w śródpiersiu pośrodkowo i po stronie lewej o największych wymiarach 65 mm [Im fuz.99]x78 [Im fuz. 108]x112 mm SUV max do 15,2.  Aktywne metabolicznie węzły chłonne: - śródpiersiowe najwyższe wielkości do 17 mm SUV max do 12,0 - zamostkowy wielkości 15x11 mm SUV max 7,2 - wnęki płuca lewego wielkości 17x11 mm SUV max 10,3 - śródpiersiowy lewy średnicy 10 mm SUV max 7,2 - przyosierdziowy prawy wielkości 5x12 mm SUV max 4,9 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwłóknienia w nadprzeponowych partiach płuc.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 6,9- odczynowo? Pobudzenie metaboliczne w macicy SUV max do 4,3- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Sklerotyczny obszar wielkości mm  w trzonie Th 5 pośrodkowo - zawał kostny ? Dyskopatia C5/6.  Wartości referencyjne: MBPS SUVmax 2,1 Prawy płat wątroby SUVmax do 4,6</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywna metabolicznie masa miękkotkankowa w śródpiersiu pośrodkowo i po stronie lewej o największych wymiarach 65 mm [Im fuz.99]x78 [Im fuz. 108]x112 mm SUV max do 15,2.  Aktywne metabolicznie węzły chłonne: - śródpiersiowe najwyższe wielkości do 17 mm SUV max do 12,0 - zamostkowy wielkości 15x11 mm SUV max 7,2 - wnęki płuca lewego wielkości 17x11 mm SUV max 10,3 - śródpiersiowy lewy średnicy 10 mm SUV max 7,2 - przyosierdziowy prawy wielkości 5x12 mm SUV max 4,9 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwłóknienia w nadprzeponowych partiach płuc.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 6,9- odczynowo? Pobudzenie metaboliczne w macicy SUV max do 4,3- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Sklerotyczny obszar wielkości mm  w trzonie Th 5 pośrodkowo - zawał kostny ? Dyskopatia C5/6.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem węzłów chłonnych śródpiersia i klatki piersiowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu pośrodkowo i po stronie lewej, o wymiarach 52x23mm, SUV max 3,9, z podejrzeniem obecności płynu w worku osierdziowym, w części górno-lewobocznej, o szerokości płaszcza do 13mm lub z jego naciekiem przez chorobę zasadniczą - dokładna ocena w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku - odczynowo? Pobudzenie metaboliczne w macicy - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym, wielkości 10x8mm.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym objętym badaniem-związane ze stosowanym leczeniem?. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny ? . Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm, SUV max do 2,3-do ew. kontroli.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 4,5.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Masa miękkotkankowa w śródpiersiu pośrodkowo i po stronie lewej, o wymiarach 52x23mm, SUV max 3,9, z podejrzeniem obecności płynu w worku osierdziowym, w części górno-lewobocznej, o szerokości płaszcza do 13mm lub z jego naciekiem przez chorobę zasadniczą - dokładna ocena w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w żołądku - odczynowo? Pobudzenie metaboliczne w macicy - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym, wielkości 10x8mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym objętym badaniem-związane ze stosowanym leczeniem?. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny ? . Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm, SUV max do 2,3-do ew. kontroli.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź procesu chłoniakowego na stosowane leczenie.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 103mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Symetryczna aktywność metaboliczna w topografii migdałków podniebiennych, SUV max do 6,9. Drobny aktywny metabolicznie węzeł chłonny grupy 2A po stronie lewej średnicy wg PET 10mm, SUV max 3,8 - odczynowy? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie lewej, o wymiarach 48x15mm (SUV max 2,8). Drobne zmiany włókniste nadprzeponowo po stronie lewej.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku, SUV max 7,9 - odczynowo? Aktywny metabolicznie obszary w poprzecznicy średnicy wg PET 15mm i 15mm, SUV max 7,7 - do rozważenia ocena endoskopowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym, wielkości 10x8mm.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?   Wartości referencyjne: MBPS SUVmax do 2,8; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Symetryczna aktywność metaboliczna w topografii migdałków podniebiennych, SUV max do 6,9. Drobny aktywny metabolicznie węzeł chłonny grupy 2A po stronie lewej średnicy wg PET 10mm, SUV max 3,8 - odczynowy? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie lewej, o wymiarach 48x15mm (SUV max 2,8). Drobne zmiany włókniste nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w żołądku, SUV max 7,9 - odczynowo? Aktywny metabolicznie obszary w poprzecznicy średnicy wg PET 15mm i 15mm, SUV max 7,7 - do rozważenia ocena endoskopowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapniony konkrement w pęcherzyku żółciowym, wielkości 10x8mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnego metabolicznie procesu chłoniakowego. Masy resztkowe do kontroli.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>7.9</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 92 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożona aktywność metaboliczna w topografii migdałków gardłowych, SUV max do 4,9. Aktywny metabolicznie węzeł chłonny szyjny grupy 2A po stronie lewej, średnicy 8 mm SUV max 4,3 - odczynowy? inny? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie lewej, z tendencją do defragmentacji, wielkości do 19x12mm (SUV max 2,1). Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne- do kontroli. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max 5,2- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x8mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?   Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 4,1.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożona aktywność metaboliczna w topografii migdałków gardłowych, SUV max do 4,9. Aktywny metabolicznie węzeł chłonny szyjny grupy 2A po stronie lewej, średnicy 8 mm SUV max 4,3 - odczynowy? inny? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie lewej, z tendencją do defragmentacji, wielkości do 19x12mm (SUV max 2,1). Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne- do kontroli. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max 5,2- odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x8mm.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywnego metabolicznie węzła chłonnego szyjnego grupy 2A  - odczynowy? inny? - niejednorodnego metabolizmu FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne - do kontroli. Masy resztkowe w śródpiersiu - do kontroli.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożona aktywność metaboliczna w topografii migdałków gardłowych, SUV max do 4,9. Aktywne metabolicznie węzły chłonne szyjne grupy 2A: po stronie lewej, średnicy 12mm SUV max 5,3, po stronie prawej średnicy 10mm, SUV max 4,4 - odczynowe? inne? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy średnicy wg PET 18mm, SUV max 9,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pobudzone metabolicznie węzeł chłonny położone przy łuku aorty średnicy wg PET do 7mm, SUV max do 2,9 [lm fuz 93] - poniżej wartości referencyjnych W śródpiersiu po stronie lewej drobne węzły chłonne wielkości do 7mm, resztkowa grasica o grubości do 8mm. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne- do kontroli. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max do 8,0 - odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x8mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?   Wartości referencyjne: MBPS SUVmax do 3,1; Prawy płat wątroby SUVmax do 4,3.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożona aktywność metaboliczna w topografii migdałków gardłowych, SUV max do 4,9. Aktywne metabolicznie węzły chłonne szyjne grupy 2A: po stronie lewej, średnicy 12mm SUV max 5,3, po stronie prawej średnicy 10mm, SUV max 4,4 - odczynowe? inne? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny podostrogowy średnicy wg PET 18mm, SUV max 9,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pobudzone metabolicznie węzeł chłonny położone przy łuku aorty średnicy wg PET do 7mm, SUV max do 2,9 [lm fuz 93] - poniżej wartości referencyjnych W śródpiersiu po stronie lewej drobne węzły chłonne wielkości do 7mm, resztkowa grasica o grubości do 8mm. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w zakresie wątroby z nieznacznie wyodrębniającymi się drobnymi obszarami w segmencie 8 i 2- zmiany niejednoznaczne- do kontroli. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max do 8,0 - odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x8mm.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Inne: Zmiany miękkotkankowe w tkance podskórnej brzucha wielkości do 10mm - poiniekcyjne?</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - aktywne metabolicznie węzły chłonne szyjne grup 2A  - odczynowe?  - pobudzone metabolicznie węzły chłonne położone przy łuku aorty oraz pojedynczy aktywny metabolicznie węzeł chłonny podostrogowy - do  weryfikacji/kontroli. Masy resztkowe w śródpiersiu - do kontroli.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>9.9</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 97 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Wzmożona aktywność metaboliczna w topografii migdałka gardłowego, SUV max do 5,9. Miernie pobudzone metabolicznie węzły chłonne szyjne grupy 2A obustronnie średnicy do 9mm, SUV max 3,3 - odczynowe? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy wielkości 22x16mm, SUV max 10,2. Nadal widoczne niejednorodny metabolizm FDG w sercu jak w badaniu przednim  - do kontroli w echokardiografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu po stronie lewej drobne węzły chłonne wielkości do 7mm, resztkowa grasica o grubości do 8mm - jak poprzednio. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x7mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 2,8; Prawy płat wątroby SUVmax do 3,9.</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Wzmożona aktywność metaboliczna w topografii migdałka gardłowego, SUV max do 5,9. Miernie pobudzone metabolicznie węzły chłonne szyjne grupy 2A obustronnie średnicy do 9mm, SUV max 3,3 - odczynowe? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny podostrogowy wielkości 22x16mm, SUV max 10,2. Nadal widoczne niejednorodny metabolizm FDG w sercu jak w badaniu przednim  - do kontroli w echokardiografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu po stronie lewej drobne węzły chłonne wielkości do 7mm, resztkowa grasica o grubości do 8mm - jak poprzednio. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w zakresie wątroby. Rozlanie wzmożony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x7mm.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzone metabolicznie węzły chłonne szyjne grup 2A  - odczynowe?  - aktywny metabolicznie węzeł chłonny podostrogowy - do  weryfikacji/kontroli. Masy resztkowe w śródpiersiu - jak w poprzednim badaniu PET/CT z dnia 8.05.2023r</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>10.2</v>
       </c>
     </row>
@@ -667,20 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 101mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>: Zwiększona aktywność metaboliczna na tylnej ścianie nosogardła, SUV max 8,5- do kontroli larynoglogicznej. Miernie pobudzone metabolicznie węzły chłonne szyjne grupy 2A obustronnie, średnicy do 9mm, SUV max 3,8 - odczynowe? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy wielkości 15x12mm, SUV max 7,9- niewielka regresja metaboliczna. Pobudzony metabolicznie węzeł chłonny w śródpiersiu po stronie lewej, wielkości 15x10mm, SUV max 3,6 (poprzednio z miernym pobudzeniem metabolicznym, SUV max 2,1). Pobudzony metabolicznie obszar miąższowo-włóknisto-guzkowy w segmencie 4 płuca lewego, wielkości ok. 13x10mm wg PET, SUV max 5,1 - do weryfikacji.  Nadal widoczny jest niejednorodny metabolizm FDG w sercu jak w badaniu przednim  - do kontroli w Echokardiografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poza powyższym w śródpiersiu przednim drobne węzły chłonne wielkości do 9mm. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.  Brzuch i miednica: Niejednorodny metabolizm FDG w zakresie wątroby. Rozlanie wzmożony metabolizm FDG w żołądku - odczynowo? Odcinkowo zwiększona aktywnośc metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x7mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax do 2,7; Prawy płat wątroby SUVmax do 4,5.</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zwiększona aktywność metaboliczna na tylnej ścianie nosogardła, SUV max 8,5- do kontroli larynoglogicznej. Miernie pobudzone metabolicznie węzły chłonne szyjne grupy 2A obustronnie, średnicy do 9mm, SUV max 3,8 - odczynowe? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Niejednorodne cieniowanie tarczycy w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny podostrogowy wielkości 15x12mm, SUV max 7,9- niewielka regresja metaboliczna. Pobudzony metabolicznie węzeł chłonny w śródpiersiu po stronie lewej, wielkości 15x10mm, SUV max 3,6 (poprzednio z miernym pobudzeniem metabolicznym, SUV max 2,1). Pobudzony metabolicznie obszar miąższowo-włóknisto-guzkowy w segmencie 4 płuca lewego, wielkości ok. 13x10mm wg PET, SUV max 5,1 - do weryfikacji.  Nadal widoczny jest niejednorodny metabolizm FDG w sercu jak w badaniu przednim  - do kontroli w Echokardiografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poza powyższym w śródpiersiu przednim drobne węzły chłonne wielkości do 9mm. Drobne zmiany włókniste w segmentach 5 obu płuc i nadprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w zakresie wątroby. Rozlanie wzmożony metabolizm FDG w żołądku - odczynowo? Odcinkowo zwiększona aktywnośc metaboliczna w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym wielkości do 10x7mm.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa - ciasna dyskopatia na poziomie C5/C6. Niejednorodny i nieregularny, sklerotyczny obszar w grzbietowej części  trzonu Th 5, wielkości ok. 14x9x16mm - zawał kostny?  Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzonych metabolicznie węzłów chłonnych szyjnych grup 2A  - odczynowe?  - aktywnego metabolicznie węzła chłonnego podostrogowo - niewielka regresja metaboliczna w stosunku do badania z 9.05.2024 - pobudzonego metabolicznie węzła chłonnego w śródpiersiu po stronie lewej. Pobudzony metabolicznie obszar miąższowo-włóknisto-guzkowy w segmencie 4 płuca lewego - do weryfikacji.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
         <v>8.5</v>
       </c>
     </row>
